--- a/tests/reports/field_validation_test_report.xlsx
+++ b/tests/reports/field_validation_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:39</t>
+          <t>2026-07-23 20:08:51</t>
         </is>
       </c>
     </row>

--- a/tests/reports/field_validation_test_report.xlsx
+++ b/tests/reports/field_validation_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:51</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
